--- a/BWI/bestwine_output/bestwine_Isle of Man.xlsx
+++ b/BWI/bestwine_output/bestwine_Isle of Man.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -937,6 +937,91 @@
       <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>30388</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1 Quines Corner</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>IM1 4LF</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.vino.co.im, https://www.vino.co.im</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>vino@vino.co.im</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>+44 1624 610968</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iomvino/</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Isle of Man.xlsx
+++ b/BWI/bestwine_output/bestwine_Isle of Man.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1022,6 +1022,91 @@
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>30388</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1 Quines Corner</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>IM1 4LF</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.vino.co.im, https://www.vino.co.im</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>vino@vino.co.im</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>+44 1624 610968</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iomvino/</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Isle of Man.xlsx
+++ b/BWI/bestwine_output/bestwine_Isle of Man.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1107,6 +1107,91 @@
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>30388</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1 Quines Corner</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>IM1 4LF</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.vino.co.im, https://www.vino.co.im</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>vino@vino.co.im</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>+44 1624 610968</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iomvino/</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Isle of Man.xlsx
+++ b/BWI/bestwine_output/bestwine_Isle of Man.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1192,6 +1192,91 @@
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>30388</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1 Quines Corner</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>IM1 4LF</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.vino.co.im, https://www.vino.co.im</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>vino@vino.co.im</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>+44 1624 610968</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iomvino/</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Isle of Man.xlsx
+++ b/BWI/bestwine_output/bestwine_Isle of Man.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1277,6 +1277,91 @@
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Vino Rewards</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>30388</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Isle of Man</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1 Quines Corner</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>IM1 4LF</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.vino.co.im, https://www.vino.co.im</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>vino@vino.co.im</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>+44 1624 610968</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iomvino/</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
